--- a/supplementary/figure11/geosmin_pathway/data/optogenetics_geosmin_pathway_251119.xlsx
+++ b/supplementary/figure11/geosmin_pathway/data/optogenetics_geosmin_pathway_251119.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Or56a" sheetId="1" state="visible" r:id="rId3"/>
@@ -17,6 +17,7 @@
     <sheet name="hortail SS41428" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="web SS41446" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="web SS41448" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="web SS41434" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="11">
   <si>
     <t xml:space="preserve">PER</t>
   </si>
@@ -72,7 +73,7 @@
     <numFmt numFmtId="165" formatCode="0.00_);[RED]\(0.00\)"/>
     <numFmt numFmtId="166" formatCode="0.0_);[RED]\(0.0\)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -95,6 +96,13 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -110,7 +118,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -125,8 +133,15 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -150,8 +165,12 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -164,26 +183,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal 2 2" xfId="20"/>
   </cellStyles>
 </styleSheet>
 </file>
@@ -688,6 +724,322 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -1731,7 +2083,7 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1745,7 +2097,7 @@
       <c r="C7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1759,7 +2111,7 @@
       <c r="C8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1773,7 +2125,7 @@
       <c r="C9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1843,7 +2195,7 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1857,7 +2209,7 @@
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1871,7 +2223,7 @@
       <c r="C16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1885,7 +2237,7 @@
       <c r="C17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1955,7 +2307,7 @@
       <c r="C22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E22" s="2"/>
@@ -1973,7 +2325,7 @@
       <c r="C23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="2"/>
@@ -1991,7 +2343,7 @@
       <c r="C24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E24" s="2"/>
@@ -2009,7 +2361,7 @@
       <c r="C25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E25" s="2"/>
@@ -2083,7 +2435,7 @@
       <c r="C30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2097,7 +2449,7 @@
       <c r="C31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2111,7 +2463,7 @@
       <c r="C32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2125,7 +2477,7 @@
       <c r="C33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2225,7 +2577,7 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2239,7 +2591,7 @@
       <c r="C7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2253,7 +2605,7 @@
       <c r="C8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2267,7 +2619,7 @@
       <c r="C9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2337,7 +2689,7 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2351,7 +2703,7 @@
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2365,7 +2717,7 @@
       <c r="C16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2379,7 +2731,7 @@
       <c r="C17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2449,7 +2801,7 @@
       <c r="C22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I22" s="2"/>
@@ -2464,7 +2816,7 @@
       <c r="C23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I23" s="2"/>
@@ -2479,7 +2831,7 @@
       <c r="C24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I24" s="2"/>
@@ -2494,7 +2846,7 @@
       <c r="C25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I25" s="2"/>
@@ -2569,7 +2921,7 @@
       <c r="C30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2583,7 +2935,7 @@
       <c r="C31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2597,7 +2949,7 @@
       <c r="C32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2611,7 +2963,7 @@
       <c r="C33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2711,7 +3063,7 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2725,7 +3077,7 @@
       <c r="C7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2739,7 +3091,7 @@
       <c r="C8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2753,7 +3105,7 @@
       <c r="C9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2823,7 +3175,7 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2837,7 +3189,7 @@
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2851,7 +3203,7 @@
       <c r="C16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2865,7 +3217,7 @@
       <c r="C17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2939,7 +3291,7 @@
       <c r="C22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I22" s="2"/>
@@ -2954,7 +3306,7 @@
       <c r="C23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="I23" s="2"/>
@@ -2969,7 +3321,7 @@
       <c r="C24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="I24" s="2"/>
@@ -2984,7 +3336,7 @@
       <c r="C25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="I25" s="2"/>
@@ -3059,7 +3411,7 @@
       <c r="C30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3073,7 +3425,7 @@
       <c r="C31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3087,7 +3439,7 @@
       <c r="C32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3101,7 +3453,7 @@
       <c r="C33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3469,7 +3821,7 @@
       <c r="C5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3483,7 +3835,7 @@
       <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3497,7 +3849,7 @@
       <c r="C7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3511,7 +3863,7 @@
       <c r="C8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3567,7 +3919,7 @@
       <c r="C12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3581,7 +3933,7 @@
       <c r="C13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3595,7 +3947,7 @@
       <c r="C14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3609,7 +3961,7 @@
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3679,7 +4031,7 @@
       <c r="C20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3693,7 +4045,7 @@
       <c r="C21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3707,7 +4059,7 @@
       <c r="C22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3721,7 +4073,7 @@
       <c r="C23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3768,7 +4120,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="B27" s="2" t="n">
@@ -3791,7 +4143,7 @@
       <c r="C28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3805,7 +4157,7 @@
       <c r="C29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3819,7 +4171,7 @@
       <c r="C30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3833,7 +4185,7 @@
       <c r="C31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="2" t="s">
         <v>10</v>
       </c>
     </row>
